--- a/Data/EXCEL/Transfer/bzPerformance/20250413PAP/2888-bzPerformance_perAndPbr20250413PAP.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/20250413PAP/2888-bzPerformance_perAndPbr20250413PAP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20250413PAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\20250413PAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B803EA05-7046-4E2D-A412-7798BE75D188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE217973-F3B3-4DC6-ABAD-6824EB57E68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{A7193723-B957-415E-BEB2-4668ADCEF943}"/>
+    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{A8C57EC4-174C-44CF-90EA-C76CC8629F62}"/>
   </bookViews>
   <sheets>
     <sheet name="2888-bzPerformance_perAndPbr202" sheetId="2" r:id="rId1"/>
@@ -1267,21 +1267,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB91A407-9ABB-4AE3-A684-92056562C0B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1850D2F-374B-4FBA-8530-62B4CC17F2E5}">
   <dimension ref="A1:Q36"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="3" width="11.77734375" customWidth="1"/>
-    <col min="4" max="6" width="12.21875" customWidth="1"/>
-    <col min="7" max="9" width="11.77734375" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" customWidth="1"/>
-    <col min="11" max="13" width="11.77734375" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" customWidth="1"/>
-    <col min="15" max="16" width="11.77734375" customWidth="1"/>
-    <col min="17" max="17" width="12" customWidth="1"/>
+    <col min="1" max="3" width="8.6328125" customWidth="1"/>
+    <col min="4" max="6" width="9.08984375" customWidth="1"/>
+    <col min="7" max="13" width="8.6328125" customWidth="1"/>
+    <col min="14" max="14" width="9.08984375" customWidth="1"/>
+    <col min="15" max="16" width="8.6328125" customWidth="1"/>
+    <col min="17" max="17" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1312,7 +1310,7 @@
       <c r="P1" s="21"/>
       <c r="Q1" s="22"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A2" s="18"/>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -1363,7 +1361,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="19"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1400,7 +1398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>2025</v>
       </c>
@@ -1453,7 +1451,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A5" s="10">
         <v>2024</v>
       </c>
@@ -1506,7 +1504,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>2023</v>
       </c>
@@ -1559,7 +1557,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A7" s="10">
         <v>2022</v>
       </c>
@@ -1612,7 +1610,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>2021</v>
       </c>
@@ -1665,7 +1663,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A9" s="10">
         <v>2020</v>
       </c>
@@ -1718,7 +1716,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>2019</v>
       </c>
@@ -1771,7 +1769,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A11" s="10">
         <v>2018</v>
       </c>
@@ -1824,7 +1822,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>2017</v>
       </c>
@@ -1877,7 +1875,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A13" s="10">
         <v>2016</v>
       </c>
@@ -1930,7 +1928,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>2015</v>
       </c>
@@ -1983,7 +1981,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A15" s="10">
         <v>2014</v>
       </c>
@@ -2036,7 +2034,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A16" s="6">
         <v>2013</v>
       </c>
@@ -2089,7 +2087,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A17" s="10">
         <v>2012</v>
       </c>
@@ -2142,7 +2140,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A18" s="6">
         <v>2011</v>
       </c>
@@ -2195,7 +2193,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A19" s="10">
         <v>2010</v>
       </c>
@@ -2248,7 +2246,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A20" s="6">
         <v>2009</v>
       </c>
@@ -2301,7 +2299,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A21" s="10">
         <v>2008</v>
       </c>
@@ -2354,7 +2352,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A22" s="6">
         <v>2007</v>
       </c>
@@ -2407,7 +2405,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A23" s="10">
         <v>2006</v>
       </c>
@@ -2460,7 +2458,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A24" s="6">
         <v>2005</v>
       </c>
@@ -2513,7 +2511,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A25" s="10">
         <v>2004</v>
       </c>
@@ -2566,7 +2564,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A26" s="6">
         <v>2003</v>
       </c>
@@ -2619,7 +2617,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A27" s="10">
         <v>2002</v>
       </c>
@@ -2672,7 +2670,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A28" s="6">
         <v>2001</v>
       </c>
@@ -2725,7 +2723,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A29" s="10">
         <v>2000</v>
       </c>
@@ -2778,7 +2776,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A30" s="6">
         <v>1999</v>
       </c>
@@ -2831,7 +2829,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A31" s="10">
         <v>1998</v>
       </c>
@@ -2884,7 +2882,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A32" s="6">
         <v>1997</v>
       </c>
@@ -2937,7 +2935,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A33" s="10">
         <v>1996</v>
       </c>
@@ -2990,7 +2988,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A34" s="6">
         <v>1995</v>
       </c>
@@ -3043,7 +3041,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A35" s="10">
         <v>1994</v>
       </c>
@@ -3096,7 +3094,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A36" s="6">
         <v>1993</v>
       </c>
